--- a/output/laminas_comunales/comunal_m_saldomigr_a_2023_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_m_saldomigr_a_2023_valparaiso.xlsx
@@ -1195,7 +1195,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2019-2023. Escala de colores estandarizada a nivel nacional para todo el periodo.</t>
+          <t>Periodo 2019-2023. Escala comunal recortada a percentiles 3-97. Sobre umbral: Villa Alemana (6.055); El Tabo (5.715); El Quisco (3.899); Algarrobo (4.528); Concón (4.904); Quintero (4.267); Puchuncaví (4.518); Limache (5.269).</t>
         </is>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_m_saldomigr_a_2023_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_m_saldomigr_a_2023_valparaiso.xlsx
@@ -1195,7 +1195,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2019-2023. Escala comunal recortada a percentiles 3-97. Sobre umbral: Villa Alemana (6.055); El Tabo (5.715); El Quisco (3.899); Algarrobo (4.528); Concón (4.904); Quintero (4.267); Puchuncaví (4.518); Limache (5.269).</t>
+          <t>Periodo 2019-2023. Escala comunal recortada a percentiles 3-97. Sobre umbral: Villa Alemana (6.055); El Tabo (5.715); El Quisco (3.899); Algarrobo (4.528); Concón (4.904); Quintero (4.267); y 2 más.</t>
         </is>
       </c>
     </row>
